--- a/internal_doc/05.测试设计/OM/数据操作/OM-数据操作（复制）-测试用例.xlsx
+++ b/internal_doc/05.测试设计/OM/数据操作/OM-数据操作（复制）-测试用例.xlsx
@@ -100,10 +100,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>复制同一条记录</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>复制字段</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -165,6 +161,10 @@
   </si>
   <si>
     <t>取消成功，记录未被复制</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>复制记录</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -704,7 +704,7 @@
     </row>
     <row r="3" spans="1:9" ht="81">
       <c r="A3" s="5" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>21</v>
@@ -713,16 +713,16 @@
         <v>2</v>
       </c>
       <c r="E3" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F3" s="4">
         <v>2</v>
       </c>
       <c r="G3" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H3" s="2" t="s">
         <v>27</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>28</v>
       </c>
       <c r="I3" s="4">
         <v>1</v>
@@ -730,7 +730,7 @@
     </row>
     <row r="4" spans="1:9" ht="81">
       <c r="A4" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>21</v>
@@ -739,16 +739,16 @@
         <v>2</v>
       </c>
       <c r="E4" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F4" s="4">
         <v>2</v>
       </c>
       <c r="G4" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" s="2" t="s">
         <v>29</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>30</v>
       </c>
       <c r="I4" s="4">
         <v>1</v>
@@ -756,25 +756,25 @@
     </row>
     <row r="5" spans="1:9" ht="94.5">
       <c r="A5" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D5" s="4">
         <v>2</v>
       </c>
       <c r="E5" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5" s="4">
         <v>2</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I5" s="4">
         <v>1</v>
@@ -782,25 +782,25 @@
     </row>
     <row r="6" spans="1:9" ht="94.5">
       <c r="A6" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C6" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" s="4">
+        <v>2</v>
+      </c>
+      <c r="E6" s="4">
+        <v>2</v>
+      </c>
+      <c r="F6" s="4">
+        <v>2</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H6" s="2" t="s">
         <v>32</v>
-      </c>
-      <c r="D6" s="4">
-        <v>2</v>
-      </c>
-      <c r="E6" s="4">
-        <v>1</v>
-      </c>
-      <c r="F6" s="4">
-        <v>2</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>33</v>
       </c>
       <c r="I6" s="4">
         <v>1</v>
@@ -808,7 +808,7 @@
     </row>
     <row r="7" spans="1:9" ht="81">
       <c r="A7" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>21</v>
@@ -823,10 +823,10 @@
         <v>2</v>
       </c>
       <c r="G7" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H7" s="2" t="s">
         <v>34</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>35</v>
       </c>
       <c r="I7" s="4">
         <v>1</v>

--- a/internal_doc/05.测试设计/OM/数据操作/OM-数据操作（复制）-测试用例.xlsx
+++ b/internal_doc/05.测试设计/OM/数据操作/OM-数据操作（复制）-测试用例.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="25">
   <si>
     <t>name</t>
   </si>
@@ -51,128 +51,82 @@
     <t>execution_type2</t>
   </si>
   <si>
-    <t>前置条件</t>
-  </si>
-  <si>
-    <t>执行步骤</t>
-  </si>
-  <si>
-    <t>期望结果</t>
-  </si>
-  <si>
-    <t>步骤执行方式（手动写1）</t>
-  </si>
-  <si>
-    <t>步骤序号（1、2、3、……）</t>
-  </si>
-  <si>
-    <t>建议为测试用例标题</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>用例执行方式（手动写1自动写2）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>重要性（1高2中3低）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>测试用例摘要（测试目的）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>标题栏文本测试</t>
+    <t>1、进入“数据库操作”页面，点击右侧操作栏中“创建集合”，检查标题栏左侧操作名和标题栏展示正确性</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>1、进入“数据库操作”页面，点击右侧操作栏中“创建集合”，检查标题栏左侧操作名和标题栏展示正确性</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>标题栏标题正确；左侧操作名正确；</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>1、数据库环境运行正常
 2、已创建集合空间、集合
 3、登录OM首页，选择集群下的“业务”，进入“业务列表”界面，选择对应业务名进入“数据”页面，选择“数据操作”进入“数据操作”页面</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>复制字段</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>集合中存在唯一索引，复制记录</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>集合中存在强制唯一索引，复制记录</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>复制记录时修改记录后‘取消’复制</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>1、点击‘集合’名链接，进入该集合列表页面
 2、点击“复制”按钮，进入复制记录弹出框界面
 3、点击“确定”复制记录</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>复制成功，返回到列表界面，列表展示复制后的记录正确</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>1、点击‘集合’名链接，进入该集合列表页面
 2、点击“复制”按钮，进入复制记录弹出框界面
 3、点击“复制”按钮复制字段
 4、点击“确定”复制记录</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>1、字段复制成功，复制后的字段展示正确
 2、记录复制成功，复制后的记录在列表展示正确</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、数据库环境运行正常
-2、已创建集合空间、集合，且存在唯一索引
-3、登录OM首页，选择集群下的“业务”，进入“业务列表”界面，选择对应业务名进入“数据”页面，选择“数据操作”进入“数据操作”页面</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>1、数据库环境运行正常
 2、已创建集合空间、集合，且存在强制唯一索引
 3、登录OM首页，选择集群下的“业务”，进入“业务列表”界面，选择对应业务名进入“数据”页面，选择“数据操作”进入“数据操作”页面</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>复制失败，页面提示索引键重复，提示信息合理准确</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>1、点击‘集合’名链接，进入该集合列表页面
 2、点击“复制”按钮，进入复制记录弹出框界面
 3、点击“取消”复制记录</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>取消成功，记录未被复制</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>复制记录</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>复制记录_om.copyRecs.001</t>
+  </si>
+  <si>
+    <t>复制字段_om.copyRecs.002</t>
+  </si>
+  <si>
+    <t>集合中存在强制唯一索引，复制记录_om.copyRecs.003</t>
+  </si>
+  <si>
+    <t>复制记录时修改记录后‘取消’复制_om.copyRecs.004</t>
+  </si>
+  <si>
+    <t>标题栏文本测试_om.copyRecs.005</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -180,12 +134,6 @@
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
@@ -220,15 +168,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
@@ -329,8 +274,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="表1_3" displayName="表1_3" ref="A1:I8" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9">
-  <autoFilter ref="A1:I8"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="表1_3" displayName="表1_3" ref="A1:I6" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9">
+  <autoFilter ref="A1:I6"/>
   <tableColumns count="9">
     <tableColumn id="1" name="name" dataDxfId="8"/>
     <tableColumn id="2" name="summary" dataDxfId="7"/>
@@ -631,11 +576,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="31.625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="30" style="5" customWidth="1"/>
+    <col min="2" max="2" width="30" style="4" customWidth="1"/>
     <col min="3" max="3" width="33.625" style="1" customWidth="1"/>
     <col min="4" max="6" width="5" style="1" customWidth="1"/>
     <col min="7" max="7" width="44.375" style="1" customWidth="1"/>
@@ -673,200 +618,139 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="36.75" customHeight="1">
-      <c r="A2" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F2" s="1" t="s">
+    <row r="2" spans="1:9" ht="81">
+      <c r="A2" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="3">
+        <v>2</v>
+      </c>
+      <c r="E2" s="3">
+        <v>3</v>
+      </c>
+      <c r="F2" s="3">
+        <v>2</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>12</v>
+      <c r="I2" s="3">
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="81">
-      <c r="A3" s="5" t="s">
-        <v>35</v>
+      <c r="A3" s="4" t="s">
+        <v>21</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D3" s="4">
-        <v>2</v>
-      </c>
-      <c r="E3" s="4">
+        <v>11</v>
+      </c>
+      <c r="D3" s="3">
+        <v>2</v>
+      </c>
+      <c r="E3" s="3">
         <v>3</v>
       </c>
-      <c r="F3" s="4">
+      <c r="F3" s="3">
         <v>2</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="I3" s="4">
+        <v>15</v>
+      </c>
+      <c r="I3" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="81">
-      <c r="A4" s="5" t="s">
+    <row r="4" spans="1:9" ht="94.5">
+      <c r="A4" s="4" t="s">
         <v>22</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D4" s="4">
-        <v>2</v>
-      </c>
-      <c r="E4" s="4">
-        <v>3</v>
-      </c>
-      <c r="F4" s="4">
+        <v>16</v>
+      </c>
+      <c r="D4" s="3">
+        <v>2</v>
+      </c>
+      <c r="E4" s="3">
+        <v>2</v>
+      </c>
+      <c r="F4" s="3">
         <v>2</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="I4" s="4">
+        <v>17</v>
+      </c>
+      <c r="I4" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="94.5">
-      <c r="A5" s="5" t="s">
+    <row r="5" spans="1:9" ht="81">
+      <c r="A5" s="4" t="s">
         <v>23</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D5" s="4">
-        <v>2</v>
-      </c>
-      <c r="E5" s="4">
-        <v>2</v>
-      </c>
-      <c r="F5" s="4">
+        <v>11</v>
+      </c>
+      <c r="D5" s="3">
+        <v>2</v>
+      </c>
+      <c r="E5" s="3">
+        <v>1</v>
+      </c>
+      <c r="F5" s="3">
         <v>2</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I5" s="4">
+        <v>19</v>
+      </c>
+      <c r="I5" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="94.5">
-      <c r="A6" s="5" t="s">
+    <row r="6" spans="1:9" ht="81">
+      <c r="A6" s="4" t="s">
         <v>24</v>
       </c>
+      <c r="B6" s="5"/>
       <c r="C6" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D6" s="4">
-        <v>2</v>
-      </c>
-      <c r="E6" s="4">
-        <v>2</v>
-      </c>
-      <c r="F6" s="4">
-        <v>2</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I6" s="4">
+        <v>11</v>
+      </c>
+      <c r="D6" s="3">
+        <v>2</v>
+      </c>
+      <c r="E6" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" ht="81">
-      <c r="A7" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D7" s="4">
-        <v>2</v>
-      </c>
-      <c r="E7" s="4">
+      <c r="F6" s="3">
+        <v>2</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I6" s="3">
         <v>1</v>
       </c>
-      <c r="F7" s="4">
-        <v>2</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="I7" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="81">
-      <c r="A8" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8" s="6"/>
-      <c r="C8" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D8" s="4">
-        <v>2</v>
-      </c>
-      <c r="E8" s="4">
-        <v>1</v>
-      </c>
-      <c r="F8" s="4">
-        <v>2</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="I8" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9">
-      <c r="A9" s="5"/>
-    </row>
-    <row r="10" spans="1:9">
-      <c r="A10" s="5"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
